--- a/output/pdf_financials_xlsx/ASTR.xlsx
+++ b/output/pdf_financials_xlsx/ASTR.xlsx
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.186648</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.300841</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.358477</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.642042</v>
       </c>
     </row>
     <row r="93">
@@ -4650,7 +4650,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -4974,7 +4978,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -5110,7 +5118,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -5572,7 +5584,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ASTR.xlsx
+++ b/output/pdf_financials_xlsx/ASTR.xlsx
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000261</v>
       </c>
     </row>
     <row r="13">
@@ -1137,7 +1137,7 @@
         <v>-1.20336</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.565363</v>
+        <v>-1.565624</v>
       </c>
     </row>
     <row r="28">
@@ -1187,7 +1187,7 @@
         <v>-1.20336</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.565363</v>
+        <v>-1.565624</v>
       </c>
     </row>
     <row r="30">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.489847</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.9063560000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.165529</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.053868</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.297636</v>
       </c>
     </row>
     <row r="35">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.489847</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.9063560000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.165529</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.053868</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.297636</v>
       </c>
     </row>
     <row r="37">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">

--- a/output/pdf_financials_xlsx/ASTR.xlsx
+++ b/output/pdf_financials_xlsx/ASTR.xlsx
@@ -3168,7 +3168,7 @@
         <v>-0.004801</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.007381</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>-0.271779</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.001953</v>
+        <v>0.005428</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0.057725</v>
@@ -4177,7 +4177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6194,10 +6194,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H44" s="5" t="n">
+        <v>-0.12598</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>-0.006457</v>
@@ -7052,15 +7050,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Shares issued for the acquisition of mineral properties</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -7071,18 +7073,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G63" s="5" t="n">
-        <v>1.455209</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0.114193</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>0.057636</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -7098,17 +7098,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Receivables</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7122,15 +7122,13 @@
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.11338</v>
+        <v>-0.009110999999999999</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.114193</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.004801</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.007381</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -7146,12 +7144,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Listing expense</t>
+          <t>Fair value of shares issued for the acquisition of non-controlling interest</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -7165,13 +7163,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G65" s="5" t="n">
-        <v>1.061783</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.218281</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -7192,17 +7190,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Receivables</t>
+          <t>Share issuance costs included in accounts payable</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7215,11 +7213,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G66" s="5" t="n">
-        <v>-0.009110999999999999</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>-0.004801</v>
+        <v>0.006457</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -7240,12 +7240,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>$    -</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Acquisition cost, RTO, net of cash acquired</t>
+          <t>Total shareholders’ equity (deficiency) 569,480 3,400,000 (132,437) 114,193 (2,850,804) 1,100,432 57,636</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -7259,18 +7259,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G67" s="5" t="n">
-        <v>-0.024403</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>-0.045292</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>-1.20336</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -7286,19 +7284,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>$    -</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Non- controlling interest $ (191,952) - - - 619,506 (427,554) - -</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -7309,8 +7303,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G68" s="5" t="n">
-        <v>-0.024403</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -7336,19 +7332,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>$    -</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
+          <t>Deficit $ (4,257,401) - - - (837,787) (2,423,250) (7,518,438) -</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -7359,18 +7351,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n">
-        <v>2.2064</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>-8.721798</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>-1.20336</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -7386,12 +7376,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>$    -</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Proceeds from option exercise</t>
+          <t>$ - - - - 57,636 - statements. Reserves 186,648 114,193</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -7405,18 +7395,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G70" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>0.358477</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>0.300841</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -7432,19 +7420,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Unit and share issuance costs</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>of part Common shares 25,106,753 21,090,910 1,455,208</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -7455,16 +7439,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n">
-        <v>-0.108214</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>-0.12598</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>47.652871</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>47.652871</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -7480,19 +7464,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cash income taxes paid</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>IncomeTaxPaidSupplementalData</t>
-        </is>
-      </c>
+          <t>Shares issued for the acquisition of mineral properties</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -7503,10 +7483,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G72" s="5" t="n">
+        <v>1.455209</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -7532,15 +7510,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Non-cash activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fair value of options exercised</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -7552,12 +7534,10 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.013582</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11338</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0.114193</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -7578,12 +7558,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Non-cash activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fair value of issued shares for the acquisition of Momentous Capital Corp.</t>
+          <t>Listing expense</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -7598,7 +7578,7 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.945</v>
+        <v>1.061783</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -7624,12 +7604,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Non-cash activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fair value of replacement stock options</t>
+          <t>Acquisition cost, RTO, net of cash acquired</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -7644,7 +7624,7 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.08685</v>
+        <v>-0.024403</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -7670,15 +7650,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Non-cash activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fair value of shares issued for the acquisition of NCI</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -7689,13 +7673,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>0.218281</v>
+      <c r="G76" s="5" t="n">
+        <v>-0.024403</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -7716,17 +7700,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Non-cash activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Share issuance costs included in accounts payable</t>
+          <t>Proceeds from issuance of common shares</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7739,13 +7723,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>0.006457</v>
+      <c r="G77" s="5" t="n">
+        <v>2.2064</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -7766,12 +7750,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>$              -</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity 338,345 2,206,400 (108,214) 1,455,209 795,000 86,850 150,000 10,000 113,380 (4,477,490) 569,480 3,400,000 (132,437) 114,193</t>
+          <t>Proceeds from option exercise</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -7786,10 +7770,12 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1.100432</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>-2.850804</v>
+        <v>0.01</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7810,15 +7796,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>$              -</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Non- controlling interest $ - - - 291,042 - - - - - (482,994) (191,952) - - 619,506 -</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Unit and share issuance costs</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -7829,13 +7819,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G79" s="5" t="n">
+        <v>-0.108214</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>-0.427554</v>
+        <v>-0.12598</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7856,15 +7844,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>$              -</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Deficit $ (262,905) - - - - - - - - (3,994,496) (4,257,401) - - (837,787) -</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Cash income taxes paid</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -7875,11 +7867,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" s="5" t="n">
-        <v>-7.518438</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>-2.42325</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7900,12 +7896,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>$              -</t>
+          <t>Non-cash activities</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>$ - - - - - 86,850 - - - - - - statements. Reserves (13,582) 113,380 186,648</t>
+          <t>Fair value of options exercised</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -7920,10 +7916,12 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.300841</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>0.114193</v>
+        <v>0.013582</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7944,12 +7942,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>Non-cash activities</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>of part Common shares 8,731,251 7,354,667 5,820,834 2,650,001 500,000 50,000 25,106,753 21,090,910</t>
+          <t>Fair value of issued shares for the acquisition of Momentous Capital Corp.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -7964,10 +7962,12 @@
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>47.652871</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>1.455208</v>
+        <v>0.945</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7988,12 +7988,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Non-cash activities</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Balance, August 24, 2020 (incorporation) - - -</t>
+          <t>Fair value of replacement stock options</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -8007,10 +8007,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G83" s="5" t="n">
+        <v>0.08685</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -8036,12 +8034,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Non-cash activities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Initial share issue on incorporation 1 - -</t>
+          <t>Fair value of shares issued for the acquisition of NCI</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -8060,10 +8058,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H84" s="5" t="n">
+        <v>0.218281</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8084,32 +8080,36 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Non-cash activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Shares issued on private placements 8,731,250 601,250 -</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Share issuance costs included in accounts payable</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>0.60125</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H85" s="5" t="n">
+        <v>0.006457</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8130,34 +8130,30 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>$              -</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Loss for the period - - -</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Total shareholders’ equity 338,345 2,206,400 (108,214) 1,455,209 795,000 86,850 150,000 10,000 113,380 (4,477,490) 569,480 3,400,000 (132,437) 114,193</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>-0.262905</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.262905</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.100432</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>-2.850804</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8178,12 +8174,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>$              -</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2021 8,731,251 601,250 -</t>
+          <t>Non- controlling interest $ - - - 291,042 - - - - - (482,994) (191,952) - - 619,506 -</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -8192,16 +8188,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>0.338345</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>-0.262905</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>-0.427554</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8222,12 +8220,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>$              -</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Shares issued on private placements 7,354,667 2,206,400 -</t>
+          <t>Deficit $ (262,905) - - - - - - - - (3,994,496) (4,257,401) - - (837,787) -</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -8236,18 +8234,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" s="5" t="n">
-        <v>2.2064</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-7.518438</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>-2.42325</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8268,12 +8264,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>$              -</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Share issuance costs - (108,214) -</t>
+          <t>$ - - - - - 86,850 - - - - - - statements. Reserves (13,582) 113,380 186,648</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -8282,18 +8278,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>-0.108214</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.300841</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>0.114193</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8314,30 +8308,30 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Shares issued to acquire mineral property interest (Note 4a) 5,820,834 1,164,167 -</t>
+          <t>of part Common shares 8,731,251 7,354,667 5,820,834 2,650,001 500,000 50,000 25,106,753 21,090,910</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
-        <v>0.291042</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>1.455209</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>47.652871</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>1.455208</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8363,7 +8357,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Shares issued for reverse takeover transaction (Note 4b) 2,650,001 795,000 -</t>
+          <t>Balance, August 24, 2020 (incorporation) - - -</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -8372,8 +8366,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>0.795</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -8409,7 +8405,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Options issued for reverse takeover transaction (Note 4b) - - 86,850</t>
+          <t>Initial share issue on incorporation 1 - -</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -8418,8 +8414,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>0.08685</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -8455,7 +8453,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Finder's shares issued for reverse takeover transaction (Note 4b) 500,000 150,000 -</t>
+          <t>Shares issued on private placements 8,731,250 601,250 -</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -8465,7 +8463,7 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.15</v>
+        <v>0.60125</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -8501,22 +8499,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of options 50,000 23,582 (13,582)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Loss for the period - - -</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.262905</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.262905</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -8547,26 +8547,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 113,380</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Balance, March 31, 2021 8,731,251 601,250 -</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.11338</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.338345</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.262905</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -8597,22 +8591,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>-0.482994</v>
+          <t>Shares issued on private placements 7,354,667 2,206,400 -</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-4.47749</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>-3.994496</v>
+        <v>2.2064</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -8643,18 +8637,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2022 25,106,753 4,832,185 186,648</t>
+          <t>Share issuance costs - (108,214) -</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>-0.191952</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.56948</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>-4.257401</v>
+        <v>-0.108214</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -8675,63 +8673,61 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares issued to acquire mineral property interest (Note 4a) 5,820,834 1,164,167 -</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" s="5" t="n">
+        <v>0.291042</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>1.455209</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H98" s="5" t="n">
-        <v>0.018747</v>
-      </c>
-      <c r="I98" s="5" t="n">
-        <v>0.004281</v>
-      </c>
-      <c r="J98" s="5" t="n">
-        <v>0.055521</v>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 5</t>
+          <t>Shares issued for reverse takeover transaction (Note 4b) 2,650,001 795,000 -</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -8740,183 +8736,187 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="5" t="n">
+        <v>0.795</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="5" t="n">
-        <v>1.378838</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>0.327192</v>
-      </c>
-      <c r="J99" s="5" t="n">
-        <v>0.475164</v>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Options issued for reverse takeover transaction (Note 4b) - - 86,850</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="5" t="n">
+        <v>0.08685</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H100" s="5" t="n">
-        <v>0.07965999999999999</v>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>0.07764500000000001</v>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>0.032862</v>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Management fees 7</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Finder's shares issued for reverse takeover transaction (Note 4b) 500,000 150,000 -</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H101" s="5" t="n">
-        <v>0.387747</v>
-      </c>
-      <c r="I101" s="5" t="n">
-        <v>0.262996</v>
-      </c>
-      <c r="J101" s="5" t="n">
-        <v>0.19125</v>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Shares issued on exercise of options 50,000 23,582 (13,582)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H102" s="5" t="n">
-        <v>0.267981</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>0.189424</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>0.239482</v>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Professional fees 7</t>
+          <t>Share-based compensation - - 113,380</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8924,114 +8924,116 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="5" t="n">
+        <v>0.11338</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H103" s="5" t="n">
-        <v>0.383607</v>
-      </c>
-      <c r="I103" s="5" t="n">
-        <v>0.199657</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>0.202182</v>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Share-based compensation 6(d),7</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>-0.482994</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>-4.47749</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>-3.994496</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="5" t="n">
-        <v>0.057636</v>
-      </c>
-      <c r="J104" s="5" t="n">
-        <v>0.280889</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Transfer agent and regulatory fees</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>0.07327400000000001</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>0.03245</v>
-      </c>
-      <c r="J105" s="5" t="n">
-        <v>0.027503</v>
+          <t>Balance, March 31, 2022 25,106,753 4,832,185 186,648</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>-0.191952</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0.56948</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>-4.257401</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -9047,7 +9049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9071,13 +9073,13 @@
         </is>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0.149888</v>
+        <v>0.018747</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.045266</v>
+        <v>0.004281</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>0.047644</v>
+        <v>0.055521</v>
       </c>
     </row>
     <row r="107">
@@ -9093,14 +9095,10 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures 5</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -9117,13 +9115,13 @@
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>2.853935</v>
+        <v>1.378838</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>1.196547</v>
+        <v>0.327192</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>1.552497</v>
+        <v>0.475164</v>
       </c>
     </row>
     <row r="108">
@@ -9134,17 +9132,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9162,16 +9160,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H108" s="5" t="n">
+        <v>0.07965999999999999</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>-0.006813</v>
+        <v>0.07764500000000001</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>-0.013127</v>
+        <v>0.032862</v>
       </c>
     </row>
     <row r="109">
@@ -9182,17 +9178,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Management fees 7</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9210,18 +9206,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H109" s="5" t="n">
+        <v>0.387747</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0.262996</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>0.000261</v>
+        <v>0.19125</v>
       </c>
     </row>
     <row r="110">
@@ -9232,17 +9224,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9255,17 +9247,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G110" s="5" t="n">
-        <v>-4.47749</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>-2.850804</v>
+        <v>0.267981</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>-1.20336</v>
+        <v>0.189424</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>-1.565363</v>
+        <v>0.239482</v>
       </c>
     </row>
     <row r="111">
@@ -9276,17 +9270,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Professional fees 7</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9299,17 +9293,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G111" s="5" t="n">
-        <v>-2.1e-07</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.383607</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.199657</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.202182</v>
       </c>
     </row>
     <row r="112">
@@ -9320,12 +9316,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Share-based compensation 6(d),7</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -9339,17 +9335,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G112" s="5" t="n">
-        <v>19.143722</v>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>35.955319</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I112" s="5" t="n">
-        <v>47.652871</v>
+        <v>0.057636</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>63.946383</v>
+        <v>0.280889</v>
       </c>
     </row>
     <row r="113">
@@ -9365,10 +9365,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Share-based compensation 7</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>Transfer agent and regulatory fees</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -9385,15 +9389,13 @@
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>0.114193</v>
+        <v>0.07327400000000001</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>0.057636</v>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03245</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0.027503</v>
       </c>
     </row>
     <row r="114">
@@ -9404,17 +9406,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Foreign exchange (loss) gain</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9433,15 +9435,13 @@
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0.003131</v>
+        <v>0.149888</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>-0.006813</v>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.045266</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0.047644</v>
       </c>
     </row>
     <row r="115">
@@ -9452,15 +9452,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Loss attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -9471,19 +9475,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" s="5" t="n">
-        <v>-3.994496</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>-2.42325</v>
+        <v>2.853935</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>-1.20336</v>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.196547</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>1.552497</v>
       </c>
     </row>
     <row r="116">
@@ -9494,17 +9498,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Loss attributable to</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Non-controlling interest 8</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -9522,18 +9526,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H116" s="5" t="n">
-        <v>0.427554</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>-0.006813</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>-0.013127</v>
       </c>
     </row>
     <row r="117">
@@ -9544,17 +9546,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9567,21 +9569,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G117" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>0.018747</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J117" s="5" t="n">
+        <v>0.000261</v>
       </c>
     </row>
     <row r="118">
@@ -9592,15 +9596,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 6</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -9612,20 +9620,16 @@
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>2.485469</v>
+        <v>-4.47749</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>1.378838</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.850804</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>-1.20336</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>-1.565363</v>
       </c>
     </row>
     <row r="119">
@@ -9636,17 +9640,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9660,20 +9664,16 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.026528</v>
+        <v>-2.1e-07</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>0.07965999999999999</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7e-08</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="120">
@@ -9684,19 +9684,15 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Management fees 8</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -9708,20 +9704,16 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.25622</v>
+        <v>19.143722</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>0.387747</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>35.955319</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>47.652871</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>63.946383</v>
       </c>
     </row>
     <row r="121">
@@ -9732,19 +9724,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Share-based compensation 7</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -9755,16 +9743,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" s="5" t="n">
-        <v>0.129064</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H121" s="5" t="n">
-        <v>0.267981</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.114193</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0.057636</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -9780,17 +9768,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Professional fees 8</t>
+          <t>Foreign exchange (loss) gain</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9803,16 +9791,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" s="5" t="n">
-        <v>0.197516</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0.383607</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003131</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>-0.006813</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -9828,12 +9816,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Loss attributable to</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Share-based compensation 8</t>
+          <t>Shareholders of the Company</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9848,15 +9836,13 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.11338</v>
+        <v>-3.994496</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0.114193</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.42325</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>-1.20336</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -9872,17 +9858,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Loss attributable to</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Transfer agent and regulatory fees</t>
+          <t>Non-controlling interest 8</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>MinorityInterests</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9895,11 +9881,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G124" s="5" t="n">
-        <v>0.084924</v>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H124" s="5" t="n">
-        <v>0.07327400000000001</v>
+        <v>0.427554</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -9925,7 +9913,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9944,10 +9932,10 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.09721399999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>0.149888</v>
+        <v>0.018747</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -9973,14 +9961,10 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures 6</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -9992,10 +9976,10 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>3.393815</v>
+        <v>2.485469</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>2.853935</v>
+        <v>1.378838</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -10016,17 +10000,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -10040,10 +10024,10 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>-0.021892</v>
+        <v>0.026528</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>0.003131</v>
+        <v>0.07965999999999999</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -10064,15 +10048,19 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Listing expense 5(b)</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>Management fees 8</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -10084,12 +10072,10 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>-1.061783</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.25622</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.387747</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -10110,17 +10096,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Loss attributable to</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Non-controlling interest 9</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -10134,10 +10120,10 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.482994</v>
+        <v>0.129064</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>0.427554</v>
+        <v>0.267981</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -10158,28 +10144,34 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" s="5" t="n">
-        <v>2.485469</v>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>0.115453</v>
+          <t>Professional fees 8</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.000511</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.197516</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>0.383607</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -10200,32 +10192,30 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>General and administrative                                                      140,667               4,673</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Management fees</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="n">
-        <v>0.25622</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>0.090583</v>
+          <t>Share-based compensation 8</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>1.1e-05</v>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11338</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>0.114193</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -10246,32 +10236,34 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Marketing                                                                      65,139              17,083</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Transfer agent and regulatory fees</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="n">
-        <v>0.235726</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>0.034566</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>1.1e-05</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.084924</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>0.07327400000000001</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -10292,17 +10284,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Marketing                                                                      65,139              17,083</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" s="5" t="n">
-        <v>0.11338</v>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10310,12 +10308,10 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.000611</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09721399999999999</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>0.149888</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -10336,17 +10332,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Foreign exchange loss                                                             21,892               547</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Listing expense</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" s="5" t="n">
-        <v>1.061783</v>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10354,12 +10356,10 @@
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.393815</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>2.853935</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -10380,41 +10380,405 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>-0.021892</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>0.003131</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Listing expense 5(b)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>-1.061783</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Loss attributable to</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Non-controlling interest 9</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.482994</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>0.427554</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" s="5" t="n">
+        <v>2.485469</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>0.115453</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.000511</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>General and administrative                                                      140,667               4,673</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.25622</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>0.090583</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>1.1e-05</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Marketing                                                                      65,139              17,083</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>0.235726</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>0.034566</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>1.1e-05</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Marketing                                                                      65,139              17,083</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" s="5" t="n">
+        <v>0.11338</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.000611</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss                                                             21,892               547</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Listing expense</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
+        <v>1.061783</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>Shareholders of the Company                                                    3,994,496             262,905</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Non-controlling interest</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>MinorityInterests</t>
         </is>
       </c>
-      <c r="E135" s="5" t="n">
+      <c r="E143" s="5" t="n">
         <v>-0.482994</v>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="n">
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="n">
         <v>-8e-06</v>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
